--- a/output/full_scan/batch_seq0_2026-07-06.xlsx
+++ b/output/full_scan/batch_seq0_2026-07-06.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O116"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8071</v>
+        <v>8996</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>612.6022669771214</v>
+        <v>629.5798085914346</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>30.95</v>
+        <v>1425</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.77853098288981</v>
+        <v>54.7056847606714</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45.47177522963502</v>
+        <v>19.87073708901666</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4311192298357241</v>
+        <v>0.2662124028038534</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.123155931427028</v>
+        <v>-11.54257189066178</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8091</v>
+        <v>8071</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>604.3841808435872</v>
+        <v>612.6022669771214</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>284.5</v>
+        <v>30.95</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>59.58031627592265</v>
+        <v>60.77853098288981</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>30.46932886237289</v>
+        <v>45.47177522963502</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.9444343074012242</v>
+        <v>0.4311192298357241</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.98126595247453</v>
+        <v>0.123155931427028</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8182</v>
+        <v>8091</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>602.6814333042093</v>
+        <v>604.3841808435872</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>55.2</v>
+        <v>284.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>58.45525187179683</v>
+        <v>59.58031627592265</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>29.07425220325946</v>
+        <v>30.46932886237289</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.8681433304209282</v>
+        <v>0.9444343074012242</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.2536900067163952</v>
+        <v>0.98126595247453</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8183</v>
+        <v>8182</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>601.0582450399085</v>
+        <v>602.6814333042093</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>34.45</v>
+        <v>55.2</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>58.41952661968291</v>
+        <v>58.45525187179683</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>24.86684936807548</v>
+        <v>29.07425220325946</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.8177403814628782</v>
+        <v>0.8681433304209282</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.2793991028527308</v>
+        <v>0.2536900067163952</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8069</v>
+        <v>8183</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>599.1313614031542</v>
+        <v>601.0582450399085</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>205.5</v>
+        <v>34.45</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>51.23939009040536</v>
+        <v>58.41952661968291</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>20.52498067194544</v>
+        <v>24.86684936807548</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8810710746974726</v>
+        <v>0.8177403814628782</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.3621879021860561</v>
+        <v>0.2793991028527308</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8105</v>
+        <v>8069</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>594.5151068984075</v>
+        <v>599.1313614031542</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>21.95</v>
+        <v>205.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.41196392851553</v>
+        <v>51.23939009040536</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>35.75328868288047</v>
+        <v>20.52498067194544</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.2317687456565669</v>
+        <v>0.8810710746974726</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.3271826676449063</v>
+        <v>0.3621879021860561</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8215</v>
+        <v>8105</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>592.1131534470668</v>
+        <v>594.5151068984075</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>30.25</v>
+        <v>21.95</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.93145482418823</v>
+        <v>54.41196392851553</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.09904182472135</v>
+        <v>35.75328868288047</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.024997379246318</v>
+        <v>0.2317687456565669</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.0978206975521127</v>
+        <v>-0.3271826676449063</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8121</v>
+        <v>8215</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>590.9044974682184</v>
+        <v>592.1131534470668</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>47.05</v>
+        <v>30.25</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.36335643281189</v>
+        <v>52.93145482418823</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>32.44469738509643</v>
+        <v>23.09904182472135</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6557382981325199</v>
+        <v>1.024997379246318</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.6901416395930298</v>
+        <v>-0.0978206975521127</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1534,21 +1534,21 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8163</v>
+        <v>8121</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>574.1773617960614</v>
+        <v>590.9044974682184</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>42.7</v>
+        <v>47.05</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>56.34253456050789</v>
+        <v>53.36335643281189</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>33.79454848986316</v>
+        <v>32.44469738509643</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6465828945608134</v>
+        <v>0.6557382981325199</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.5599133912811791</v>
+        <v>-0.6901416395930298</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8476</v>
+        <v>8163</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>562.5955542714083</v>
+        <v>574.1773617960614</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>23.95</v>
+        <v>42.7</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>75.09242922774419</v>
+        <v>56.34253456050789</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>59.42044650511445</v>
+        <v>33.79454848986316</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8741096347625487</v>
+        <v>0.6465828945608134</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1106117138496496</v>
+        <v>-0.5599133912811791</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8261</v>
+        <v>8476</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>557.0774444926718</v>
+        <v>562.5955542714083</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>352</v>
+        <v>23.95</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>81.5317114769697</v>
+        <v>75.09242922774419</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>52.67861009097644</v>
+        <v>59.42044650511445</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.23214955411215</v>
+        <v>0.8741096347625487</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>11.1171479629769</v>
+        <v>0.1106117138496496</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8488</v>
+        <v>8261</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>554.4133608115937</v>
+        <v>557.0774444926718</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>10.2</v>
+        <v>352</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.83995076657783</v>
+        <v>81.5317114769697</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>14.14878968376473</v>
+        <v>52.67861009097644</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.1058370920200596</v>
+        <v>0.23214955411215</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0188297253297868</v>
+        <v>11.1171479629769</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8442</v>
+        <v>8488</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>550.1651707212387</v>
+        <v>554.4133608115937</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>42.7</v>
+        <v>10.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.1901113059839</v>
+        <v>51.83995076657783</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>27.17587828436562</v>
+        <v>14.14878968376473</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5347175210068802</v>
+        <v>0.1058370920200596</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.4938225303306649</v>
+        <v>0.0188297253297868</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>9912</v>
+        <v>8442</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>549.4143149389733</v>
+        <v>550.1651707212387</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>12.7</v>
+        <v>42.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>59.20218816562105</v>
+        <v>56.1901113059839</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28.0021623058025</v>
+        <v>27.17587828436562</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5414314938973283</v>
+        <v>0.5347175210068802</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0171036805057079</v>
+        <v>0.4938225303306649</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8084</v>
+        <v>9912</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>548.5660418093947</v>
+        <v>549.4143149389733</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>49.75</v>
+        <v>12.7</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>57.54479850999557</v>
+        <v>59.20218816562105</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18.93306665428147</v>
+        <v>28.0021623058025</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.544808377986958</v>
+        <v>0.5414314938973283</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.0394258362829449</v>
+        <v>0.0171036805057079</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>9905</v>
+        <v>8084</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>534.2562258319053</v>
+        <v>548.5660418093947</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>21.35</v>
+        <v>49.75</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>64.82671347142164</v>
+        <v>57.54479850999557</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.51273501352532</v>
+        <v>18.93306665428147</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.462429580080081</v>
+        <v>1.544808377986958</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0422303072508006</v>
+        <v>-0.0394258362829449</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8222</v>
+        <v>9905</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>531.2187491004129</v>
+        <v>534.2562258319053</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>43.8</v>
+        <v>21.35</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>70.19308146043846</v>
+        <v>64.82671347142164</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>24.33273167888343</v>
+        <v>23.51273501352532</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.228160215707488</v>
+        <v>1.462429580080081</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.012416231154139</v>
+        <v>0.0422303072508006</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8050</v>
+        <v>8222</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>530.7776065125581</v>
+        <v>531.2187491004129</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>57</v>
+        <v>43.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>58.62755952388817</v>
+        <v>70.19308146043846</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>26.75644141528212</v>
+        <v>24.33273167888343</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.9088043563401352</v>
+        <v>6.228160215707488</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.1817598236499286</v>
+        <v>1.012416231154139</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8049</v>
+        <v>8050</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>527.1134527926929</v>
+        <v>530.7776065125581</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>27.15</v>
+        <v>57</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>50.45511841360729</v>
+        <v>58.62755952388817</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>27.31217114119925</v>
+        <v>26.75644141528212</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.405547117759632</v>
+        <v>0.9088043563401352</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.0837498235079859</v>
+        <v>-0.1817598236499286</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8067</v>
+        <v>8049</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>523.5539897121181</v>
+        <v>527.1134527926929</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>14.2</v>
+        <v>27.15</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>55.31623027129852</v>
+        <v>50.45511841360729</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>8.285682700375734</v>
+        <v>27.31217114119925</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.0568981985669892</v>
+        <v>0.405547117759632</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0100119216688447</v>
+        <v>-0.0837498235079859</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8462</v>
+        <v>8067</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>516.1088872577246</v>
+        <v>523.5539897121181</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>151</v>
+        <v>14.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>66.87031162283432</v>
+        <v>55.31623027129852</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>21.45818037895786</v>
+        <v>8.285682700375734</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.131544172161093</v>
+        <v>0.0568981985669892</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.149426230498104</v>
+        <v>0.0100119216688447</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8454</v>
+        <v>8462</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>514.4102987905462</v>
+        <v>516.1088872577246</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>281</v>
+        <v>151</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>45.47765673170429</v>
+        <v>66.87031162283432</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>37.01963995148049</v>
+        <v>21.45818037895786</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.603599631978047</v>
+        <v>1.131544172161093</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-12.16335507460641</v>
+        <v>1.149426230498104</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8411</v>
+        <v>8454</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>513.1666955854625</v>
+        <v>514.4102987905462</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>12.4</v>
+        <v>281</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>60.13927391392479</v>
+        <v>45.47765673170429</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>33.91809275800525</v>
+        <v>37.01963995148049</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4125865744237179</v>
+        <v>0.603599631978047</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0377435662533966</v>
+        <v>-12.16335507460641</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8289</v>
+        <v>8411</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>507.0469415616991</v>
+        <v>513.1666955854625</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>63.5</v>
+        <v>12.4</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.05710968031797</v>
+        <v>60.13927391392479</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.01236791957148</v>
+        <v>33.91809275800525</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7850434648745941</v>
+        <v>0.4125865744237179</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.4523750787151865</v>
+        <v>0.0377435662533966</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8926</v>
+        <v>8289</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>503.3012929762153</v>
+        <v>507.0469415616991</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>81</v>
+        <v>63.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>64.174232844888</v>
+        <v>51.05710968031797</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>41.86266809206205</v>
+        <v>20.01236791957148</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.113435783026859</v>
+        <v>0.7850434648745941</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.8653058280910884</v>
+        <v>-0.4523750787151865</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8089</v>
+        <v>8926</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>502.362636796964</v>
+        <v>503.3012929762153</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>20.75</v>
+        <v>81</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.1794973615081</v>
+        <v>64.174232844888</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>29.72784635219124</v>
+        <v>41.86266809206205</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.176667306645519</v>
+        <v>1.113435783026859</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.001771891502672</v>
+        <v>-0.8653058280910884</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8088</v>
+        <v>8089</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>497.6718623026623</v>
+        <v>502.362636796964</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>60.8</v>
+        <v>20.75</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>47.89477475545366</v>
+        <v>52.1794973615081</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.02906570970961</v>
+        <v>29.72784635219124</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4044197198460776</v>
+        <v>1.176667306645519</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.9315880319955164</v>
+        <v>0.001771891502672</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8070</v>
+        <v>8088</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>495.97804183942</v>
+        <v>497.6718623026623</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>57.2</v>
+        <v>60.8</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>56.51964453762154</v>
+        <v>47.89477475545366</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>22.53931558574896</v>
+        <v>20.02906570970961</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.149426511259364</v>
+        <v>0.4044197198460776</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.3402389064965994</v>
+        <v>-0.9315880319955164</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8464</v>
+        <v>8070</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>474.9718791806</v>
+        <v>495.97804183942</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>370</v>
+        <v>57.2</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>62.37689746539153</v>
+        <v>56.51964453762154</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.3919927325692</v>
+        <v>22.53931558574896</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5427537507994158</v>
+        <v>1.149426511259364</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>2.561421970687697</v>
+        <v>-0.3402389064965994</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8076</v>
+        <v>8464</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>472.9811458525601</v>
+        <v>474.9718791806</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>26.3</v>
+        <v>370</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>58.37131849134606</v>
+        <v>62.37689746539153</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15.29808007722908</v>
+        <v>22.3919927325692</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.9813020098371688</v>
+        <v>0.5427537507994158</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0266029952065863</v>
+        <v>2.561421970687697</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>9105</v>
+        <v>8076</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>472.2163130546247</v>
+        <v>472.9811458525601</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>9.199999999999999</v>
+        <v>26.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>50.74381957636155</v>
+        <v>58.37131849134606</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>33.23282436654442</v>
+        <v>15.29808007722908</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.4601119121547501</v>
+        <v>0.9813020098371688</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.1710198257081162</v>
+        <v>-0.0266029952065863</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8093</v>
+        <v>9105</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>470.9536225343844</v>
+        <v>472.2163130546247</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.83828799758298</v>
+        <v>50.74381957636155</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>9.937183253789939</v>
+        <v>33.23282436654442</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.431057174779357</v>
+        <v>0.4601119121547501</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1995887899666374</v>
+        <v>-0.1710198257081162</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8176</v>
+        <v>8093</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>462.4445345243545</v>
+        <v>470.9536225343844</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>10.85</v>
+        <v>20</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>63.84428617454708</v>
+        <v>53.83828799758298</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.69570049740644</v>
+        <v>9.937183253789939</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.584255109323073</v>
+        <v>1.431057174779357</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0962438875009486</v>
+        <v>0.1995887899666374</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8104</v>
+        <v>8176</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>460.4267332160196</v>
+        <v>462.4445345243545</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>41.25</v>
+        <v>10.85</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>58.35552501298656</v>
+        <v>63.84428617454708</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.93764906974737</v>
+        <v>19.69570049740644</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.730520854319028</v>
+        <v>1.584255109323073</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.1901588652903634</v>
+        <v>0.0962438875009486</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8072</v>
+        <v>8104</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>459.9037186213943</v>
+        <v>460.4267332160196</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>29.3</v>
+        <v>41.25</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.73322079250963</v>
+        <v>58.35552501298656</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>23.76725711122995</v>
+        <v>19.93764906974737</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.66791508530993</v>
+        <v>1.730520854319028</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0519570883903176</v>
+        <v>-0.1901588652903634</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8481</v>
+        <v>8072</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>452.5509517841264</v>
+        <v>459.9037186213943</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>42.1</v>
+        <v>29.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>61.36690870509538</v>
+        <v>50.73322079250963</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>19.0968022060592</v>
+        <v>23.76725711122995</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.20726409825699</v>
+        <v>0.66791508530993</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0062599364678224</v>
+        <v>-0.0519570883903176</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8147</v>
+        <v>8481</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>443.3768236853</v>
+        <v>452.5509517841264</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>157.5</v>
+        <v>42.1</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>55.13849512729062</v>
+        <v>61.36690870509538</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19.38249040932356</v>
+        <v>19.0968022060592</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.359113382457558</v>
+        <v>1.20726409825699</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>2.10432504518108</v>
+        <v>-0.0062599364678224</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8422</v>
+        <v>8147</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>440.1065580453582</v>
+        <v>443.3768236853</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>28.6</v>
+        <v>157.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>53.6065627482107</v>
+        <v>55.13849512729062</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>13.86795748830356</v>
+        <v>19.38249040932356</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.165584958486288</v>
+        <v>1.359113382457558</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.058584420525808</v>
+        <v>2.10432504518108</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8234</v>
+        <v>8422</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>438.8386240296355</v>
+        <v>440.1065580453582</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>71</v>
+        <v>28.6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.61512739484071</v>
+        <v>53.6065627482107</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>24.02239017793365</v>
+        <v>13.86795748830356</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.8355388023719503</v>
+        <v>1.165584958486288</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.6960368890616729</v>
+        <v>-0.058584420525808</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8227</v>
+        <v>8234</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>422.9080876272152</v>
+        <v>438.8386240296355</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>201</v>
+        <v>71</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.24195477781554</v>
+        <v>54.61512739484071</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>15.7733747726501</v>
+        <v>24.02239017793365</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.864412854083801</v>
+        <v>0.8355388023719503</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>1</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>2.01555233305305</v>
+        <v>0.6960368890616729</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8473</v>
+        <v>8227</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>415.7540714823707</v>
+        <v>422.9080876272152</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>48.6</v>
+        <v>201</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.3923771244658</v>
+        <v>52.24195477781554</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>23.49283843238738</v>
+        <v>15.7733747726501</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2939593560374657</v>
+        <v>0.864412854083801</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.6733100010089976</v>
+        <v>2.01555233305305</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8358</v>
+        <v>8473</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>411.3870641934139</v>
+        <v>415.7540714823707</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>563</v>
+        <v>48.6</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>47.65830887743527</v>
+        <v>50.3923771244658</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16.47787612764211</v>
+        <v>23.49283843238738</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.270636680097774</v>
+        <v>0.2939593560374657</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-13.56822925990755</v>
+        <v>-0.6733100010089976</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8112</v>
+        <v>8358</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>407.5004635268191</v>
+        <v>411.3870641934139</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>89.5</v>
+        <v>563</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.85289670527558</v>
+        <v>47.65830887743527</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>19.77644606728681</v>
+        <v>16.47787612764211</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6149594157319752</v>
+        <v>1.270636680097774</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-1.014283061699441</v>
+        <v>-13.56822925990755</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8068</v>
+        <v>8112</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>407.0354024757312</v>
+        <v>407.5004635268191</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>19.2</v>
+        <v>89.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>47.16421148385754</v>
+        <v>45.85289670527558</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16.88316487274984</v>
+        <v>19.77644606728681</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.5397413679498606</v>
+        <v>0.6149594157319752</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.1341630334942239</v>
+        <v>-1.014283061699441</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8155</v>
+        <v>8068</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>406.5597365946438</v>
+        <v>407.0354024757312</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>373.5</v>
+        <v>19.2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45.7737898059942</v>
+        <v>47.16421148385754</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.37046519134671</v>
+        <v>16.88316487274984</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5625198087656729</v>
+        <v>0.5397413679498606</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.6114494295383079</v>
+        <v>0.1341630334942239</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8110</v>
+        <v>8155</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>406.5284332146076</v>
+        <v>406.5597365946438</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>54.6</v>
+        <v>373.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>47.44398846570103</v>
+        <v>45.7737898059942</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16.64700596965693</v>
+        <v>15.37046519134671</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.5313772453205672</v>
+        <v>0.5625198087656729</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.7395451444495351</v>
+        <v>-0.6114494295383079</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3548,21 +3548,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8271</v>
+        <v>8110</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>405.3529132804969</v>
+        <v>406.5284332146076</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>196</v>
+        <v>54.6</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.50011372686126</v>
+        <v>47.44398846570103</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.54988865159727</v>
+        <v>16.64700596965693</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6851246252260983</v>
+        <v>0.5313772453205672</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.012861352171708</v>
+        <v>-0.7395451444495351</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3601,21 +3601,21 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8291</v>
+        <v>8271</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>398.991270675896</v>
+        <v>405.3529132804969</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>36.20904001722542</v>
+        <v>43.50011372686126</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>27.00341312717991</v>
+        <v>19.54988865159727</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2895075219198775</v>
+        <v>0.6851246252260983</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-1.232563324743802</v>
+        <v>-1.012861352171708</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>9906</v>
+        <v>8291</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>398.3151798565003</v>
+        <v>398.991270675896</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>42.9</v>
+        <v>37</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>55.54456599916365</v>
+        <v>36.20904001722542</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>36.348008255335</v>
+        <v>27.00341312717991</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3003068506166121</v>
+        <v>0.2895075219198775</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.328778269488583</v>
+        <v>-1.232563324743802</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8466</v>
+        <v>9906</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>393.1577588906839</v>
+        <v>398.3151798565003</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>17.3</v>
+        <v>42.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>64.12418057628315</v>
+        <v>55.54456599916365</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>24.35504175773394</v>
+        <v>36.348008255335</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.8197376583295676</v>
+        <v>0.3003068506166121</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1733740153463496</v>
+        <v>-0.328778269488583</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>9911</v>
+        <v>8466</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>374.9727620146476</v>
+        <v>393.1577588906839</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>84.5</v>
+        <v>17.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>56.78559243091347</v>
+        <v>64.12418057628315</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>13.73301819933622</v>
+        <v>24.35504175773394</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.380374025051924</v>
+        <v>0.8197376583295676</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1791648431216765</v>
+        <v>0.1733740153463496</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>9136</v>
+        <v>9911</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>372.6599105645645</v>
+        <v>374.9727620146476</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>13.45</v>
+        <v>84.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.13483186768888</v>
+        <v>56.78559243091347</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>33.68569421694865</v>
+        <v>13.73301819933622</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.3253730842200272</v>
+        <v>1.380374025051924</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.6701599121394397</v>
+        <v>0.1791648431216765</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8097</v>
+        <v>9136</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>370.9273547072983</v>
+        <v>372.6599105645645</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>57.5</v>
+        <v>13.45</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46.34590549257489</v>
+        <v>48.13483186768888</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>18.43964143296433</v>
+        <v>33.68569421694865</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5151147978997732</v>
+        <v>0.3253730842200272</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.3648118138652008</v>
+        <v>-0.6701599121394397</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8054</v>
+        <v>8097</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>368.8088025737597</v>
+        <v>370.9273547072983</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>109.5</v>
+        <v>57.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>48.08895135607558</v>
+        <v>46.34590549257489</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.58973676613008</v>
+        <v>18.43964143296433</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5414801098918665</v>
+        <v>0.5151147978997732</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.5697155563093825</v>
+        <v>-0.3648118138652008</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8443</v>
+        <v>8054</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>362.8720632457589</v>
+        <v>368.8088025737597</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>11.45</v>
+        <v>109.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.40700979352444</v>
+        <v>48.08895135607558</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>48.19710445383507</v>
+        <v>22.58973676613008</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3872063245758885</v>
+        <v>0.5414801098918665</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0134714431857754</v>
+        <v>-0.5697155563093825</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8103</v>
+        <v>8443</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>359.0895349322618</v>
+        <v>362.8720632457589</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>102.5</v>
+        <v>11.45</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>52.62859412953105</v>
+        <v>50.40700979352444</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.34380465795764</v>
+        <v>48.19710445383507</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6931164687237471</v>
+        <v>0.3872063245758885</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1.032704377773617</v>
+        <v>0.0134714431857754</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8482</v>
+        <v>8103</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>339.8399372401163</v>
+        <v>359.0895349322618</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>49.25</v>
+        <v>102.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.86607548546366</v>
+        <v>52.62859412953105</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7.084230390667521</v>
+        <v>14.34380465795764</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4254232961796987</v>
+        <v>0.6931164687237471</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>2.06680159645681</v>
+        <v>1.032704377773617</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8390</v>
+        <v>8482</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>335.4745783391224</v>
+        <v>339.8399372401163</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>107</v>
+        <v>49.25</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>44.58894194854894</v>
+        <v>51.86607548546366</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>20.81469920672741</v>
+        <v>7.084230390667521</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.372786468164978</v>
+        <v>0.4254232961796987</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.9224475523760488</v>
+        <v>2.06680159645681</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8463</v>
+        <v>8390</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>333.5235272135785</v>
+        <v>335.4745783391224</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>21.75</v>
+        <v>107</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.75440418864147</v>
+        <v>44.58894194854894</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>13.55791469654413</v>
+        <v>20.81469920672741</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.284741883911827</v>
+        <v>0.372786468164978</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0208086487923314</v>
+        <v>-0.9224475523760488</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8086</v>
+        <v>8463</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>328.8541328954822</v>
+        <v>333.5235272135785</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>144.5</v>
+        <v>21.75</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.63606071796613</v>
+        <v>51.75440418864147</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>13.7075288998941</v>
+        <v>13.55791469654413</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.9183969102758114</v>
+        <v>1.284741883911827</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-1.429767364868911</v>
+        <v>0.0208086487923314</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8367</v>
+        <v>8086</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>328.6651579276064</v>
+        <v>328.8541328954822</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>40.5</v>
+        <v>144.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>48.9649454767465</v>
+        <v>43.63606071796613</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23.33425547545483</v>
+        <v>13.7075288998941</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9529569736887796</v>
+        <v>0.9183969102758114</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.07782432033938549</v>
+        <v>-1.429767364868911</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8299</v>
+        <v>8367</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>327.6060990489838</v>
+        <v>328.6651579276064</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>2290</v>
+        <v>40.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,49 +4368,49 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>46.50439517021095</v>
+        <v>48.9649454767465</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>11.45278076272503</v>
+        <v>23.33425547545483</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.827951210020172</v>
+        <v>0.9529569736887796</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-21.43248700565141</v>
+        <v>0.07782432033938549</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8478</v>
+        <v>8299</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>322.7190785295309</v>
+        <v>327.6060990489838</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>162</v>
+        <v>2290</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,49 +4421,49 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>60.61802384451487</v>
+        <v>46.50439517021095</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14.97014249029196</v>
+        <v>11.45278076272503</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.071907852953084</v>
+        <v>0.827951210020172</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>1.270417657758081</v>
+        <v>-21.43248700565141</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8240</v>
+        <v>8478</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>322.4287600851617</v>
+        <v>322.7190785295309</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>52.7</v>
+        <v>162</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>39.94863047368042</v>
+        <v>60.61802384451487</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15.55850192004144</v>
+        <v>14.97014249029196</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6018167895503095</v>
+        <v>2.071907852953084</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.0691015861002264</v>
+        <v>1.270417657758081</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8201</v>
+        <v>8240</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>309.6026701296632</v>
+        <v>322.4287600851617</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>13.25</v>
+        <v>52.7</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>50.72062043382648</v>
+        <v>39.94863047368042</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>19.07317996738509</v>
+        <v>15.55850192004144</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7051550230306782</v>
+        <v>0.6018167895503095</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0134983061241461</v>
+        <v>-0.0691015861002264</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8059</v>
+        <v>8201</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>293.1446014313618</v>
+        <v>309.6026701296632</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>16.6</v>
+        <v>13.25</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>37.64955842697944</v>
+        <v>50.72062043382648</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.3166943387881</v>
+        <v>19.07317996738509</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.115836443014648</v>
+        <v>0.7051550230306782</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0066758139028837</v>
+        <v>-0.0134983061241461</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>9930</v>
+        <v>8059</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>291.5728448873994</v>
+        <v>293.1446014313618</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>64.2</v>
+        <v>16.6</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>21.92447126274106</v>
+        <v>37.64955842697944</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>33.1549147224929</v>
+        <v>22.3166943387881</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.865309041600504</v>
+        <v>1.115836443014648</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.4603568501874626</v>
+        <v>0.0066758139028837</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8341</v>
+        <v>9930</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>290.8977918489959</v>
+        <v>291.5728448873994</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>77</v>
+        <v>64.2</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46.12502544047726</v>
+        <v>21.92447126274106</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20.43454884461237</v>
+        <v>33.1549147224929</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7974371446211679</v>
+        <v>1.865309041600504</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.3961863250440725</v>
+        <v>-0.4603568501874626</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8277</v>
+        <v>8341</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>288.0356433014427</v>
+        <v>290.8977918489959</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>8.93</v>
+        <v>77</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.68584493803085</v>
+        <v>46.12502544047726</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>24.18271698744816</v>
+        <v>20.43454884461237</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.8984832976644646</v>
+        <v>0.7974371446211679</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.2816798225018795</v>
+        <v>-0.3961863250440725</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8102</v>
+        <v>8277</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>285.7021148501287</v>
+        <v>288.0356433014427</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.16511398174988</v>
+        <v>42.68584493803085</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17.30755850358145</v>
+        <v>24.18271698744816</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4892776398505141</v>
+        <v>0.8984832976644646</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.7024067186921643</v>
+        <v>-0.2816798225018795</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8080</v>
+        <v>8102</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>284.520974034232</v>
+        <v>285.7021148501287</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>27.85</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>47.46833648129793</v>
+        <v>43.16511398174988</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46.34012691382776</v>
+        <v>17.30755850358145</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.404387942144475</v>
+        <v>0.4892776398505141</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0201626237718851</v>
+        <v>-0.7024067186921643</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8374</v>
+        <v>8080</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>280.3745543966991</v>
+        <v>284.520974034232</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>92.09999999999999</v>
+        <v>27.85</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>50.87358443969304</v>
+        <v>47.46833648129793</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>14.65889299210469</v>
+        <v>46.34012691382776</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.7599456025913665</v>
+        <v>1.404387942144475</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.3750346786302532</v>
+        <v>-0.0201626237718851</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>9904</v>
+        <v>8374</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>273.3559058685448</v>
+        <v>280.3745543966991</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>24.35</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>31.03103567891755</v>
+        <v>50.87358443969304</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>20.48805548639409</v>
+        <v>14.65889299210469</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7355905868544848</v>
+        <v>0.7599456025913665</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.1890955277394513</v>
+        <v>0.3750346786302532</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>9955</v>
+        <v>9904</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>255.806242342029</v>
+        <v>273.3559058685448</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>27.15</v>
+        <v>24.35</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.41835901238781</v>
+        <v>31.03103567891755</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21.5214727613168</v>
+        <v>20.48805548639409</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.9022068665175424</v>
+        <v>0.7355905868544848</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1113966238897757</v>
+        <v>-0.1890955277394513</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8074</v>
+        <v>9955</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>254.0746811813341</v>
+        <v>255.8062423420289</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>68.5</v>
+        <v>27.15</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.81757520965808</v>
+        <v>48.41835901238781</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.91333245982166</v>
+        <v>21.5214727613168</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4625130977603557</v>
+        <v>0.9022068665175424</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.2607633117095167</v>
+        <v>0.1113966238897757</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8472</v>
+        <v>8074</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>252.1125374758637</v>
+        <v>254.0746811813341</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>82.7</v>
+        <v>68.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>50.4542049588725</v>
+        <v>44.81757520965808</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.06542856603911</v>
+        <v>11.91333245982166</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4045253216943308</v>
+        <v>0.4625130977603557</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.8622838970466207</v>
+        <v>-0.2607633117095167</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>9110</v>
+        <v>8472</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>250.6473300370583</v>
+        <v>252.1125374758637</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>3.36</v>
+        <v>82.7</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>52.04645948714767</v>
+        <v>50.4542049588725</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13.10520072797411</v>
+        <v>16.06542856603911</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8840926012815195</v>
+        <v>0.4045253216943308</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0641554793038101</v>
+        <v>-0.8622838970466207</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>9907</v>
+        <v>9110</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>247.8939656847285</v>
+        <v>250.6473300370583</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>15.4</v>
+        <v>3.36</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.92082608999376</v>
+        <v>52.04645948714767</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>26.74003253719274</v>
+        <v>13.10520072797411</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4996492773097774</v>
+        <v>0.8840926012815195</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0126682901381594</v>
+        <v>0.0641554793038101</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8111</v>
+        <v>9907</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>240.7847683403797</v>
+        <v>247.8939656847285</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>52.9</v>
+        <v>15.4</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>38.46267712560378</v>
+        <v>41.92082608999376</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>24.31513834526347</v>
+        <v>26.74003253719274</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6613058732800072</v>
+        <v>0.4996492773097774</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1552418840548339</v>
+        <v>-0.0126682901381594</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8423</v>
+        <v>8111</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>237.8185681650269</v>
+        <v>240.7847683403797</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>17.75</v>
+        <v>52.9</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>49.7462402989611</v>
+        <v>38.46267712560378</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>10.90913337598509</v>
+        <v>24.31513834526347</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.505892086491805</v>
+        <v>0.6613058732800072</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.009915539235020501</v>
+        <v>0.1552418840548339</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8431</v>
+        <v>8423</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>232.8837969128656</v>
+        <v>237.8185681650269</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>53.3</v>
+        <v>17.75</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>47.09248131262092</v>
+        <v>49.7462402989611</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>10.58181379376996</v>
+        <v>10.90913337598509</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4836874143528264</v>
+        <v>1.505892086491805</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.1771987889756674</v>
+        <v>0.009915539235020501</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>9103</v>
+        <v>8431</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>226.8165296416724</v>
+        <v>232.8837969128656</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>5.18</v>
+        <v>53.3</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.44626815156568</v>
+        <v>47.09248131262092</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17.68376000072078</v>
+        <v>10.58181379376996</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4351754444160119</v>
+        <v>0.4836874143528264</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0354851021071751</v>
+        <v>0.1771987889756674</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8087</v>
+        <v>9103</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>217.2455218274085</v>
+        <v>226.8165296416724</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>31.9</v>
+        <v>5.18</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40.64570469239143</v>
+        <v>46.44626815156568</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>11.71264945459337</v>
+        <v>17.68376000072078</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4483113117941868</v>
+        <v>0.4351754444160119</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.2093597943281719</v>
+        <v>-0.0354851021071751</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8048</v>
+        <v>8087</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>212.0311457132216</v>
+        <v>217.2455218274085</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>62.1</v>
+        <v>31.9</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>46.89660822186213</v>
+        <v>40.64570469239143</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.22933133144842</v>
+        <v>11.71264945459337</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.402431388732768</v>
+        <v>0.4483113117941868</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.3768550951376028</v>
+        <v>-0.2093597943281719</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8210</v>
+        <v>8048</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>207.2343478674488</v>
+        <v>212.0311457132216</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>1290</v>
+        <v>62.1</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45.99115243309642</v>
+        <v>46.89660822186213</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.77398535015331</v>
+        <v>13.22933133144842</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.3777153398334776</v>
+        <v>0.402431388732768</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-8.650802795626227</v>
+        <v>-0.3768550951376028</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8455</v>
+        <v>8210</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>207.0334693070444</v>
+        <v>207.2343478674488</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>27.9</v>
+        <v>1290</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.72641627722628</v>
+        <v>45.99115243309642</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.68160325753023</v>
+        <v>13.77398535015331</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4772624515146467</v>
+        <v>0.3777153398334776</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.2028124439202503</v>
+        <v>-8.650802795626227</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8404</v>
+        <v>8455</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>204.5648722517932</v>
+        <v>207.0334693070444</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>16.9</v>
+        <v>27.9</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.82457867914178</v>
+        <v>42.72641627722628</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>12.85278852732761</v>
+        <v>17.68160325753023</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6874480240272286</v>
+        <v>0.4772624515146467</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0373941666205882</v>
+        <v>-0.2028124439202503</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8114</v>
+        <v>8404</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>201.0184852077249</v>
+        <v>204.5648722517932</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>205.5</v>
+        <v>16.9</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>50.03124874472774</v>
+        <v>51.82457867914178</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.26466867531428</v>
+        <v>12.85278852732761</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7317555913419559</v>
+        <v>0.6874480240272286</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.0080135005366273</v>
+        <v>0.0373941666205882</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8940</v>
+        <v>8114</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>200.6846043257129</v>
+        <v>201.0184852077249</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>16.8</v>
+        <v>205.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.90028860232989</v>
+        <v>50.03124874472774</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.60433254446836</v>
+        <v>20.26466867531428</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5371227699998642</v>
+        <v>0.7317555913419559</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0426020875118156</v>
+        <v>-0.0080135005366273</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8213</v>
+        <v>8940</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>194.5970302012014</v>
+        <v>200.6846043257129</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>35.9</v>
+        <v>16.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.25043534916151</v>
+        <v>51.90028860232989</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>12.33016834453989</v>
+        <v>17.60433254446836</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4971488863453466</v>
+        <v>0.5371227699998642</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0347859458489525</v>
+        <v>0.0426020875118156</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>9910</v>
+        <v>8213</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>177.7275946700958</v>
+        <v>194.5970302012014</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>69.2</v>
+        <v>35.9</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.78212680813621</v>
+        <v>45.25043534916151</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.83159505129877</v>
+        <v>12.33016834453989</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.252991384663192</v>
+        <v>0.4971488863453466</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.8763447424336754</v>
+        <v>-0.0347859458489525</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8429</v>
+        <v>9910</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>177.2021758388342</v>
+        <v>177.7275946700958</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>6.47</v>
+        <v>69.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>53.78723693688073</v>
+        <v>42.78212680813621</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.80925779118407</v>
+        <v>18.83159505129877</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.069600110696001</v>
+        <v>0.252991384663192</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0008551079158636</v>
+        <v>-0.8763447424336754</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8477</v>
+        <v>8429</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>163.9389145424554</v>
+        <v>177.2021758388342</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>16</v>
+        <v>6.47</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>41.76658890111302</v>
+        <v>53.78723693688073</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.09451337273189</v>
+        <v>16.80925779118407</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6811588881136856</v>
+        <v>1.069600110696001</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2114004358457979</v>
+        <v>0.0008551079158636</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8410</v>
+        <v>8477</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>154.0819745219743</v>
+        <v>163.9389145424554</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>33.25</v>
+        <v>16</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.83897980491916</v>
+        <v>41.76658890111302</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.3779211494526</v>
+        <v>18.09451337273189</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.8010981304925175</v>
+        <v>0.6811588881136856</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.1080985111307269</v>
+        <v>-0.2114004358457979</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8101</v>
+        <v>8410</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>152.743996789687</v>
+        <v>154.0819745219743</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>13.3</v>
+        <v>33.25</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.52436590866338</v>
+        <v>44.83897980491916</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.2574175417573</v>
+        <v>16.3779211494526</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.325973739884369</v>
+        <v>0.8010981304925175</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1582349584103384</v>
+        <v>0.1080985111307269</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8249</v>
+        <v>8101</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>142.168337369156</v>
+        <v>152.743996789687</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>49.1</v>
+        <v>13.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.93693776039009</v>
+        <v>44.52436590866338</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15.03718494852895</v>
+        <v>12.2574175417573</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6925891888707966</v>
+        <v>1.325973739884369</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1706269235569206</v>
+        <v>-0.1582349584103384</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8440</v>
+        <v>8249</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>137.16400206452</v>
+        <v>142.168337369156</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>22</v>
+        <v>49.1</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>49.35276432411652</v>
+        <v>44.93693776039009</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>9.987898756516582</v>
+        <v>15.03718494852895</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.256899968707625</v>
+        <v>0.6925891888707966</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0014042499814109</v>
+        <v>-0.1706269235569206</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8467</v>
+        <v>8440</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>133.148586476889</v>
+        <v>137.16400206452</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>47.02086701036004</v>
+        <v>49.35276432411652</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>10.47082113366944</v>
+        <v>9.987898756516582</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.746777742331208</v>
+        <v>1.256899968707625</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1591693342383453</v>
+        <v>-0.0014042499814109</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>9802</v>
+        <v>8467</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>117.6125777619453</v>
+        <v>133.148586476889</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>74.8</v>
+        <v>114</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.44982861437393</v>
+        <v>47.02086701036004</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>15.91040907014925</v>
+        <v>10.47082113366944</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5725929665231791</v>
+        <v>1.746777742331208</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1531048816832962</v>
+        <v>0.1591693342383453</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8171</v>
+        <v>9802</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>101.2243138073925</v>
+        <v>117.6125777619453</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>21.65</v>
+        <v>74.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.99342423081311</v>
+        <v>46.44982861437393</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.17823548447196</v>
+        <v>15.91040907014925</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.405364999051885</v>
+        <v>0.5725929665231791</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0580700945731659</v>
+        <v>-0.1531048816832962</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>9902</v>
+        <v>8171</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>100.9936275850659</v>
+        <v>101.2243138073925</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>13.95</v>
+        <v>21.65</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>52.75801083000282</v>
+        <v>46.99342423081311</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>15.14287580922342</v>
+        <v>19.17823548447196</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>3.021261912421924</v>
+        <v>0.405364999051885</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0584352125737534</v>
+        <v>0.0580700945731659</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8487</v>
+        <v>9902</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>86.32873197244079</v>
+        <v>100.9936275850659</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>78.3</v>
+        <v>13.95</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>46.36265240381756</v>
+        <v>52.75801083000282</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.05073383581213</v>
+        <v>15.14287580922342</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4446326641733222</v>
+        <v>3.021261912421924</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.1205867759576403</v>
+        <v>0.0584352125737534</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8092</v>
+        <v>8487</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>80.01899985048388</v>
+        <v>86.32873197244079</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>14.6</v>
+        <v>78.3</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>47.2305912151346</v>
+        <v>46.36265240381756</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.2115193619866</v>
+        <v>11.05073383581213</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>2.328806245386218</v>
+        <v>0.4446326641733222</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,62 +6559,115 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0704904090851612</v>
+        <v>-0.1205867759576403</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
+        <v>8092</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>建暐</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>80.01899985048388</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>47.2305912151346</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>19.2115193619866</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>2.328806245386218</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.0704904090851612</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>8085</v>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>福華</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>15.11157147965997</v>
       </c>
-      <c r="E116" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>12.25</v>
       </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
         <v>47.619546610193</v>
       </c>
-      <c r="I116" s="2" t="n">
+      <c r="I117" s="2" t="n">
         <v>15.80861717438109</v>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J117" s="2" t="n">
         <v>0.3090482358350492</v>
       </c>
-      <c r="K116" s="2" t="n">
+      <c r="K117" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
         <v>-0.0241157069751214</v>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60</t>
         </is>
